--- a/assets/fonte/criticas_pre_processamento_5050.xlsx
+++ b/assets/fonte/criticas_pre_processamento_5050.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\Fonte DRO - 5050\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\conversor_dro_5050 3\assets\fonte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9E44ED-25A3-4A14-B466-11C5C790FC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857016CB-CD67-4613-B805-CCDE88B18CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9120" yWindow="345" windowWidth="31005" windowHeight="17355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3285" yWindow="2880" windowWidth="24675" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Criticas Pre" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="82">
   <si>
     <t>Código</t>
   </si>
@@ -265,6 +265,12 @@
   </si>
   <si>
     <t>Verifica a inexistência de informação nos campos de informações contábeis, por indevida, nos casos de um idEvento que contenha lançamentos relativos apenas a risco. Ou seja, não é devida a informação de conta contábil nos casos de um contexto de informações exclusivas a valores em risco. O bloco XML "contabilizacao" não deve ser informado.</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Coluna1</t>
   </si>
 </sst>
 </file>
@@ -423,14 +429,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="CriticasPreProcessamento" displayName="CriticasPreProcessamento" ref="A1:F35">
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="CriticasPreProcessamento" displayName="CriticasPreProcessamento" ref="A1:G35">
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Código"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Doc"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Tipo"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Descrição"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Base Confrontada"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Data-início"/>
+    <tableColumn id="7" xr3:uid="{1A46084D-ED99-495A-B6C5-BBD3DE1DAE8D}" name="Coluna1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -585,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -596,7 +603,7 @@
     <col min="6" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="26.1" customHeight="1">
+    <row r="1" spans="1:7" ht="26.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -615,8 +622,11 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -636,7 +646,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="28.5">
+    <row r="3" spans="1:7" ht="28.5">
       <c r="A3" s="7" t="s">
         <v>12</v>
       </c>
@@ -656,7 +666,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="28.5">
+    <row r="4" spans="1:7" ht="28.5">
       <c r="A4" s="7" t="s">
         <v>14</v>
       </c>
@@ -676,7 +686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="28.5">
+    <row r="5" spans="1:7" ht="28.5">
       <c r="A5" s="7" t="s">
         <v>17</v>
       </c>
@@ -696,7 +706,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6" s="7" t="s">
         <v>19</v>
       </c>
@@ -716,7 +726,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="28.5">
+    <row r="7" spans="1:7" ht="28.5">
       <c r="A7" s="7" t="s">
         <v>21</v>
       </c>
@@ -735,8 +745,11 @@
       <c r="F7" s="12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="28.5">
+      <c r="G7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="28.5">
       <c r="A8" s="7" t="s">
         <v>23</v>
       </c>
@@ -755,8 +768,11 @@
       <c r="F8" s="12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="28.5">
+      <c r="G8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="28.5">
       <c r="A9" s="7" t="s">
         <v>25</v>
       </c>
@@ -776,7 +792,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="42.75">
+    <row r="10" spans="1:7" ht="42.75">
       <c r="A10" s="7" t="s">
         <v>27</v>
       </c>
@@ -796,7 +812,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="28.5">
+    <row r="11" spans="1:7" ht="28.5">
       <c r="A11" s="7" t="s">
         <v>29</v>
       </c>
@@ -816,7 +832,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="28.5">
+    <row r="12" spans="1:7" ht="28.5">
       <c r="A12" s="7" t="s">
         <v>31</v>
       </c>
@@ -836,7 +852,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="57">
+    <row r="13" spans="1:7" ht="57">
       <c r="A13" s="7" t="s">
         <v>33</v>
       </c>
@@ -856,7 +872,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="28.5">
+    <row r="14" spans="1:7" ht="28.5">
       <c r="A14" s="7" t="s">
         <v>35</v>
       </c>
@@ -876,7 +892,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="28.5">
+    <row r="15" spans="1:7" ht="28.5">
       <c r="A15" s="7" t="s">
         <v>37</v>
       </c>
@@ -896,7 +912,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="28.5">
+    <row r="16" spans="1:7" ht="28.5">
       <c r="A16" s="7" t="s">
         <v>39</v>
       </c>
@@ -916,7 +932,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="28.5">
+    <row r="17" spans="1:7" ht="28.5">
       <c r="A17" s="7" t="s">
         <v>41</v>
       </c>
@@ -935,8 +951,11 @@
       <c r="F17" s="12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="28.5">
+      <c r="G17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="28.5">
       <c r="A18" s="7" t="s">
         <v>43</v>
       </c>
@@ -956,7 +975,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="42.75">
+    <row r="19" spans="1:7" ht="42.75">
       <c r="A19" s="7" t="s">
         <v>45</v>
       </c>
@@ -976,7 +995,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="42.75">
+    <row r="20" spans="1:7" ht="42.75">
       <c r="A20" s="7" t="s">
         <v>47</v>
       </c>
@@ -996,7 +1015,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="57">
+    <row r="21" spans="1:7" ht="57">
       <c r="A21" s="7" t="s">
         <v>49</v>
       </c>
@@ -1016,7 +1035,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="57">
+    <row r="22" spans="1:7" ht="57">
       <c r="A22" s="7" t="s">
         <v>51</v>
       </c>
@@ -1036,7 +1055,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="42.75">
+    <row r="23" spans="1:7" ht="42.75">
       <c r="A23" s="7" t="s">
         <v>53</v>
       </c>
@@ -1056,7 +1075,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="42.75">
+    <row r="24" spans="1:7" ht="42.75">
       <c r="A24" s="7" t="s">
         <v>55</v>
       </c>
@@ -1076,7 +1095,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="42.75">
+    <row r="25" spans="1:7" ht="42.75">
       <c r="A25" s="7" t="s">
         <v>57</v>
       </c>
@@ -1096,7 +1115,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="28.5">
+    <row r="26" spans="1:7" ht="28.5">
       <c r="A26" s="7" t="s">
         <v>59</v>
       </c>
@@ -1115,8 +1134,11 @@
       <c r="F26" s="12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="42.75">
+      <c r="G26" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="42.75">
       <c r="A27" s="7" t="s">
         <v>61</v>
       </c>
@@ -1135,8 +1157,11 @@
       <c r="F27" s="12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" ht="28.5">
+      <c r="G27" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="28.5">
       <c r="A28" s="7" t="s">
         <v>63</v>
       </c>
@@ -1156,7 +1181,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="28.5">
+    <row r="29" spans="1:7" ht="28.5">
       <c r="A29" s="7" t="s">
         <v>66</v>
       </c>
@@ -1176,7 +1201,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="33" customHeight="1">
+    <row r="30" spans="1:7" ht="33" customHeight="1">
       <c r="A30" s="7" t="s">
         <v>68</v>
       </c>
@@ -1196,7 +1221,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="33.75" customHeight="1">
+    <row r="31" spans="1:7" ht="33.75" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>70</v>
       </c>
@@ -1216,7 +1241,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="42.75">
+    <row r="32" spans="1:7" ht="42.75">
       <c r="A32" s="7" t="s">
         <v>72</v>
       </c>
@@ -1235,8 +1260,11 @@
       <c r="F32" s="12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" ht="46.5" customHeight="1">
+      <c r="G32" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="46.5" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>74</v>
       </c>
@@ -1255,8 +1283,11 @@
       <c r="F33" s="12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" ht="62.25" customHeight="1">
+      <c r="G33" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="62.25" customHeight="1">
       <c r="A34" s="7" t="s">
         <v>76</v>
       </c>
@@ -1276,7 +1307,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="71.25">
+    <row r="35" spans="1:7" ht="71.25">
       <c r="A35" s="9" t="s">
         <v>78</v>
       </c>
